--- a/AI토플_오프라인동기화_전략.xlsx
+++ b/AI토플_오프라인동기화_전략.xlsx
@@ -59,12 +59,12 @@
       <name val="Apple SD Gothic Neo"/>
       <color rgb="FF0B6E5F"/>
       <sz val="11"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Apple SD Gothic Neo"/>
       <color rgb="FF0B6E5F"/>
       <sz val="11"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Apple SD Gothic Neo"/>
@@ -140,10 +140,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -519,33 +519,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D26"/>
+  <dimension ref="B2:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SMEAG STUDYGROUND · 데이터 전략</t>
+          <t>SMEAG STUDYGROUND · 데이터 전략 · rev 2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>인터넷이 없는 교실에서 답안을 잃지 않는 법</t>
+          <t>시험이 끝나고 3분, 그 안에 답안을 회수한다</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>아래 파란 글씨를 클릭하면 해당 자료가 열립니다.</t>
+          <t>아래 초록 글씨를 클릭하면 해당 자료가 열립니다.</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>시험은 오프라인, 동기화는 인터넷 복귀 후 자동.</t>
+          <t>시험 중 차단 · 종료 직후 회수 · 허브 없음.</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>세 가지 원칙</t>
+          <t>확정된 전제</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>네트워크는 시험을 멈추지 않는다 · 정본은 로컬 · 두 번 보내도 안전.</t>
+          <t>인터넷은 평소엔 됨 · 공용 PC · 30명 75–150MB (병목 아님).</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>데이터가 지나가는 길</t>
+          <t>회수창 — 종료 후 3분</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>학생 PC → 교실 허브 → ⟂인터넷⟂ → Supabase → 대시보드.</t>
+          <t>종료 → 회선 개통 → 30대 동시 업로드 → 완료 게이트 → 로컬 삭제.</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>교실 허브를 둘 것인가</t>
+          <t>고아 아웃박스</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>A안은 답안 사본 한 벌, B안은 두 벌. 단말 초기화 시 결과가 갈린다.</t>
+          <t>★ 공용 PC 의 진짜 문제. 앞 반 큐를 아무도 안 읽는다.</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>권장 결정</t>
+          <t>결론 — 각자 올린다</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>B안 채택. 단 허브가 죽으면 단말이 Supabase 로 직접 가도록 A안도 살려둔다.</t>
+          <t>허브 대신 3가지: 고아 회수 · 완료 게이트 · 확인 후 삭제.</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>로컬 저장 → 전송 대기 → 전송 중 → 동기화 완료 → 확정 채점. 3회 실패는 미제출.</t>
+          <t>로컬 저장 → 전송 대기 → 전송 중 → 동기화 완료 → 확정 채점 → 로컬 삭제.</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>오프라인 잠정 점수 + 서버 확정 재채점. 불일치는 조작 탐지 신호.</t>
+          <t>오프라인 잠정 + 서버 확정. 불일치는 조작 탐지 신호.</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>지금 빠진 것 5가지</t>
+          <t>지금 빠진 것 6가지</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>치명은 하나 — A안에서 시험 후 PC 초기화.</t>
+          <t>치명은 하나 — 공용 PC 게스트 모드/복원 프로그램.</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>롤아웃 5단계</t>
+          <t>롤아웃 4단계</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>단계 2 완료 시점이 “선생님이 채점 완료를 본다”가 성립하는 지점.</t>
+          <t>단계 3 완료 시점이 “선생님이 채점 완료를 본다”가 성립하는 지점.</t>
         </is>
       </c>
     </row>
@@ -756,19 +756,19 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>코딩 전 결정 4가지</t>
+          <t>코딩 전 확인 4가지</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>허브 채택 · 계정 발급 시점 · 녹음 총량 · 저장소 공개 범위.</t>
+          <t>PC 관리 방식 · 3분 확보 · 계정 발급 시점 · 저장소 공개 범위.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>원본 코드 근거</t>
+          <t>원본 코드 근거 (실측)</t>
         </is>
       </c>
     </row>
@@ -782,30 +782,38 @@
     <row r="24">
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>studyground/sg2/assets/exam-store.js — localStorage/IndexedDB 지속성 (구현됨)</t>
+          <t>studyground/sg2/assets/exam-store.js — 세션별 키 분리 · allKeys() · IndexedDB 녹음 (구현됨)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>app/js/sync.js — Supabase 직접 업로드 경로 (구현됨, 위와 미통합)</t>
+          <t>studyground/sg2/config/timing.toefl.json — SR 12문항 8–12초, Interview 4문항 45초</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="14" t="inlineStr">
         <is>
+          <t>app/js/sync.js — Supabase 직접 업로드 경로 (구현됨, 위와 미통합)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="14" t="inlineStr">
+        <is>
           <t>supabase/schema.sql — 테이블 · RLS (교사 역할 정책 없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId1"/>

--- a/AI토플_오프라인동기화_전략.xlsx
+++ b/AI토플_오프라인동기화_전략.xlsx
@@ -35,7 +35,7 @@
       <name val="Apple SD Gothic Neo"/>
       <b val="1"/>
       <color rgb="FF101715"/>
-      <sz val="20"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Apple SD Gothic Neo"/>
@@ -519,26 +519,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D27"/>
+  <dimension ref="B2:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="82" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SMEAG STUDYGROUND · 데이터 전략 · rev 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>SMEAG STUDYGROUND · 데이터 전략 · rev 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>시험이 끝나고 3분, 그 안에 답안을 회수한다</t>
+          <t>회선과 무관하게 시험을 치고, 끝나면 녹음까지 자동으로 올린다</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>시험 중 차단 · 종료 직후 회수 · 허브 없음.</t>
+          <t>회선 무관 실행 · 종료 후 녹음까지 자동 회수.</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>확정된 전제</t>
+          <t>완성 조건 넷</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>인터넷은 평소엔 됨 · 공용 PC · 30명 75–150MB (병목 아님).</t>
+          <t>실행 · 응시는 이미 됨 / 회수 · 녹음은 이번에 만든다.</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>회수창 — 종료 후 3분</t>
+          <t>확정된 전제</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>종료 → 회선 개통 → 30대 동시 업로드 → 완료 게이트 → 로컬 삭제.</t>
+          <t>인터넷 평소엔 됨 · 공용 PC · 30명 75–150MB (병목 아님).</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>고아 아웃박스</t>
+          <t>회선 무관 실행</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>★ 공용 PC 의 진짜 문제. 앞 반 큐를 아무도 안 읽는다.</t>
+          <t>앱 셸·문항·오디오·채점 전부 로컬. 네트워크 호출 0회.</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>결론 — 각자 올린다</t>
+          <t>저장 3중화</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>허브 대신 3가지: 고아 회수 · 완료 게이트 · 확인 후 삭제.</t>
+          <t>★ 브라우저 저장소 · 디스크 폴더 · 내보내기 파일. 게스트 모드 대응.</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>답안 한 건의 일생</t>
+          <t>게스트 모드 대안 순위</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>로컬 저장 → 전송 대기 → 전송 중 → 동기화 완료 → 확정 채점 → 로컬 삭제.</t>
+          <t>프로필 예외 → Supabase 화이트리스트 → 폴더 저장 → 데스크톱 앱.</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>채점은 두 번 한다</t>
+          <t>녹음 파일이 가는 길</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>오프라인 잠정 + 서버 확정. 불일치는 조작 탐지 신호.</t>
+          <t>IndexedDB → base64 → Storage &lt;uid&gt;/&lt;attempt&gt;/&lt;qid&gt;.webm.</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>지금 빠진 것 6가지</t>
+          <t>회수창 — 종료 후 3분</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>★ 교사용 RLS 부재가 요구사항의 핵심 병목.</t>
+          <t>종료 → 회선 개통 → 답안·녹음 업로드 → 완료 게이트 → 로컬 삭제.</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>실패 시나리오</t>
+          <t>고아 아웃박스</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>치명은 하나 — 공용 PC 게스트 모드/복원 프로그램.</t>
+          <t>★ 앞 반 큐를 아무도 안 읽는다. 전체 세션 스캔으로 해결.</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>롤아웃 4단계</t>
+          <t>답안 한 건의 일생</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>단계 3 완료 시점이 “선생님이 채점 완료를 본다”가 성립하는 지점.</t>
+          <t>동기화 완료는 답안+녹음 모두 확인된 뒤에만. 그 뒤 로컬 3겹 삭제.</t>
         </is>
       </c>
     </row>
@@ -756,64 +756,132 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>코딩 전 확인 4가지</t>
+          <t>채점은 두 번 한다</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>PC 관리 방식 · 3분 확보 · 계정 발급 시점 · 저장소 공개 범위.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="13" t="inlineStr">
+          <t>오프라인 잠정 + 서버 확정. 불일치는 조작 탐지 신호.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="B21" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>지금 빠진 것 7가지</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>★ 교사용 RLS 부재 · 내보내기에 녹음 누락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="B22" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>실패 시나리오</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>치명은 하나 — 게스트 모드인데 계층 ②·③ 도 없을 때.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="B23" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>롤아웃 6단계</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>단계 1(녹음 동봉 내보내기)은 지금 바로 시작 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="B24" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>병행 확인 5가지</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>PC 모드 · 공유기 · 3분 확보 · 계정 발급 · 저장소 공개 범위.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>원본 코드 근거 (실측)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>studyground/sg2/assets/exam-sync.js — Outbox · 지수 백오프 · JSON 내보내기 (구현됨)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>studyground/sg2/assets/exam-store.js — 세션별 키 분리 · allKeys() · IndexedDB 녹음 (구현됨)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>studyground/sg2/config/timing.toefl.json — SR 12문항 8–12초, Interview 4문항 45초</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>app/js/sync.js — Supabase 직접 업로드 경로 (구현됨, 위와 미통합)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>supabase/schema.sql — 테이블 · RLS (교사 역할 정책 없음)</t>
+          <t>studyground/sg2/sw.js — 앱 셸 프리캐시 · 오프라인 실행 (구현됨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>studyground/sg2/assets/exam-sync.js — Outbox · 백오프 · downloadExport (녹음 미포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>studyground/sg2/assets/exam-store.js — 세션별 키 · allKeys() · IndexedDB 녹음 (구현됨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>studyground/sg2/config/timing.toefl.json — SR 12문항 8–12초, Interview 4문항 45초</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>app/js/sync.js — Supabase 직접 업로드 경로 (구현됨, 위와 미통합)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>supabase/schema.sql — 테이블 · RLS · toefl-recordings 버킷 (교사 역할 정책 없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
+  <mergeCells count="6">
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C32:D32"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C31:D31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId1"/>
@@ -829,6 +897,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
